--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +620,7 @@
       <c r="T2" t="n">
         <v>12.18</v>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +707,7 @@
       <c r="T3" t="n">
         <v>16.97</v>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -787,6 +794,7 @@
       <c r="T4" t="n">
         <v>-100</v>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -873,6 +881,7 @@
       <c r="T5" t="n">
         <v>11.59</v>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,6 +968,7 @@
       <c r="T6" t="n">
         <v>5.42</v>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,6 +1055,7 @@
       <c r="T7" t="n">
         <v>15.32</v>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1131,6 +1142,7 @@
       <c r="T8" t="n">
         <v>15.84</v>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1217,6 +1229,7 @@
       <c r="T9" t="n">
         <v>16.97</v>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1303,6 +1316,7 @@
       <c r="T10" t="n">
         <v>16.38</v>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1389,6 +1403,7 @@
       <c r="T11" t="n">
         <v>16.38</v>
       </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1475,6 +1490,7 @@
       <c r="T12" t="n">
         <v>15.32</v>
       </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1561,6 +1577,7 @@
       <c r="T13" t="n">
         <v>5.14</v>
       </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1647,6 +1664,7 @@
       <c r="T14" t="n">
         <v>17.59</v>
       </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,6 +1751,7 @@
       <c r="T15" t="n">
         <v>13.58</v>
       </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1819,6 +1838,7 @@
       <c r="T16" t="n">
         <v>14.39</v>
       </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1905,6 +1925,7 @@
       <c r="T17" t="n">
         <v>12.18</v>
       </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1991,6 +2012,7 @@
       <c r="T18" t="n">
         <v>15.32</v>
       </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2000,37 +2022,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ponte Preta x Sao Bernardo</t>
+          <t>Lanus x Defensa y Justicia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2039,43 +2061,42 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>11.11</v>
+        <v>9.52</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.95</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>10.55</v>
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9.19</v>
       </c>
     </row>
     <row r="20">
@@ -2091,32 +2112,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportivo Tachira x Rayo Zuliano</t>
+          <t>Ponte Preta x Sao Bernardo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Tachira</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2125,20 +2146,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="L20" t="n">
-        <v>14.71</v>
+        <v>11.11</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2161,8 +2182,9 @@
         <v>0.95</v>
       </c>
       <c r="T20" t="n">
-        <v>13.97</v>
-      </c>
+        <v>10.55</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2172,27 +2194,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The Strongest x Real Tomayapo</t>
+          <t>Deportivo Tachira x Rayo Zuliano</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Deportivo Tachira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2211,13 +2233,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="K21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="L21" t="n">
-        <v>12.2</v>
+        <v>14.71</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -2247,8 +2269,9 @@
         <v>0.95</v>
       </c>
       <c r="T21" t="n">
-        <v>11.59</v>
-      </c>
+        <v>13.97</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2258,27 +2281,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cruz Azul x Santos Laguna</t>
+          <t>The Strongest x Real Tomayapo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2297,20 +2320,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="L22" t="n">
-        <v>20.41</v>
+        <v>12.2</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2333,8 +2356,9 @@
         <v>0.95</v>
       </c>
       <c r="T22" t="n">
-        <v>19.39</v>
-      </c>
+        <v>11.59</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2344,27 +2368,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportivo Pereira x Millonarios</t>
+          <t>Cruz Azul x Santos Laguna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2383,44 +2407,45 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K23" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="L23" t="n">
-        <v>21.74</v>
+        <v>20.41</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6</v>
+        <v>0.95</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>-4.6</v>
+        <v>0.95</v>
       </c>
       <c r="T23" t="n">
-        <v>-100</v>
-      </c>
+        <v>19.39</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2430,27 +2455,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Melgar x Asociacion Deportiva Tarma</t>
+          <t>Deportivo Pereira x Millonarios</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Melgar</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asociacion Deportiva Tarma</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2469,43 +2494,303 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="L24" t="n">
-        <v>23.26</v>
+        <v>21.74</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Melgar x Asociacion Deportiva Tarma</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Asociacion Deportiva Tarma</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>3x0</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="Q25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T25" t="n">
         <v>22.1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca x Libertad FC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="M26" t="n">
+        <v>200</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Dep. Cuenca x Libertad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dep. Cuenca</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="M27" t="n">
+        <v>200</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="T27" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="U27" t="n">
+        <v>10.16</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-06.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2074,19 +2074,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2681,19 +2681,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S26" t="n">
